--- a/final_data_pipeline/output/325110longform_elec_options.xlsx
+++ b/final_data_pipeline/output/325110longform_elec_options.xlsx
@@ -669,7 +669,7 @@
         <v>66</v>
       </c>
       <c r="K2">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L2">
         <v>8000</v>
@@ -684,10 +684,10 @@
         <v>169.4098799338086</v>
       </c>
       <c r="R2">
-        <v>1.025288461538461</v>
+        <v>1.03592820319873</v>
       </c>
       <c r="S2">
-        <v>1.0563</v>
+        <v>1.067704754529766</v>
       </c>
       <c r="T2">
         <v>0.02117623499172607</v>
@@ -722,7 +722,7 @@
         <v>67</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L3">
         <v>8000</v>
@@ -769,7 +769,7 @@
         <v>67</v>
       </c>
       <c r="K4">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="L4">
         <v>8000</v>
@@ -816,7 +816,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="L5">
         <v>8000</v>
@@ -831,10 +831,10 @@
         <v>32995.30490400347</v>
       </c>
       <c r="R5">
-        <v>1.025288461538461</v>
+        <v>0.9939102066179896</v>
       </c>
       <c r="S5">
-        <v>1.0563</v>
+        <v>1.022720671292561</v>
       </c>
       <c r="T5">
         <v>4.124413113000434</v>
@@ -869,7 +869,7 @@
         <v>67</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="L6">
         <v>8000</v>
@@ -2891,7 +2891,7 @@
         <v>67</v>
       </c>
       <c r="K48">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="L48">
         <v>8000</v>
@@ -2938,7 +2938,7 @@
         <v>67</v>
       </c>
       <c r="K49">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="L49">
         <v>8000</v>
@@ -2985,7 +2985,7 @@
         <v>66</v>
       </c>
       <c r="K50">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="L50">
         <v>8000</v>
@@ -3000,10 +3000,10 @@
         <v>651265.6796054139</v>
       </c>
       <c r="R50">
-        <v>1.025288461538461</v>
+        <v>1.064821081830791</v>
       </c>
       <c r="S50">
-        <v>1.0563</v>
+        <v>1.098722912453048</v>
       </c>
       <c r="T50">
         <v>81.40820995067673</v>
@@ -3038,7 +3038,7 @@
         <v>66</v>
       </c>
       <c r="K51">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="L51">
         <v>8000</v>
@@ -3053,10 +3053,10 @@
         <v>77758.08985627412</v>
       </c>
       <c r="R51">
-        <v>1.025288461538461</v>
+        <v>1.069250338898071</v>
       </c>
       <c r="S51">
-        <v>1.0563</v>
+        <v>1.103484165522044</v>
       </c>
       <c r="T51">
         <v>9.719761232034266</v>
@@ -3091,7 +3091,7 @@
         <v>67</v>
       </c>
       <c r="K52">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="L52">
         <v>8000</v>
@@ -4613,7 +4613,7 @@
         <v>67</v>
       </c>
       <c r="K84">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L84">
         <v>8000</v>
@@ -4707,7 +4707,7 @@
         <v>67</v>
       </c>
       <c r="K86">
-        <v>10</v>
+        <v>20.22222222222222</v>
       </c>
       <c r="L86">
         <v>8000</v>
